--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J369"/>
+  <dimension ref="A1:J370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13728,6 +13728,42 @@
       <c r="J369" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="C370" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="D370" t="n">
+        <v>390.08</v>
+      </c>
+      <c r="E370" t="n">
+        <v>391.81</v>
+      </c>
+      <c r="F370" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="G370" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="H370" t="n">
+        <v>387.61</v>
+      </c>
+      <c r="I370" t="n">
+        <v>384.54</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B388"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17625,6 +17661,16 @@
       </c>
       <c r="B388" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -17793,28 +17839,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1500722257351629</v>
+        <v>0.1499336948152963</v>
       </c>
       <c r="J2" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05840397051548263</v>
+        <v>0.05862556117121553</v>
       </c>
       <c r="M2" t="n">
-        <v>3.440476136065376</v>
+        <v>3.431818872286606</v>
       </c>
       <c r="N2" t="n">
-        <v>19.998705128799</v>
+        <v>19.94468794763343</v>
       </c>
       <c r="O2" t="n">
-        <v>4.47199118165488</v>
+        <v>4.465947597949783</v>
       </c>
       <c r="P2" t="n">
-        <v>381.4361812326468</v>
+        <v>381.4375997442826</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17871,28 +17917,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.174849620368886</v>
+        <v>0.1715500140204397</v>
       </c>
       <c r="J3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06258558495135313</v>
+        <v>0.06049096743423088</v>
       </c>
       <c r="M3" t="n">
-        <v>4.094114406829551</v>
+        <v>4.099901408754627</v>
       </c>
       <c r="N3" t="n">
-        <v>25.2211963704878</v>
+        <v>25.25488035499406</v>
       </c>
       <c r="O3" t="n">
-        <v>5.022070924478048</v>
+        <v>5.025423400569752</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4362767909889</v>
+        <v>381.4700636885503</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17949,28 +17995,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1413144610755887</v>
+        <v>0.1406098650762428</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K4" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04462482951727431</v>
+        <v>0.04444115382874203</v>
       </c>
       <c r="M4" t="n">
-        <v>3.935076644300466</v>
+        <v>3.928039897753937</v>
       </c>
       <c r="N4" t="n">
-        <v>23.54775873907214</v>
+        <v>23.488596336338</v>
       </c>
       <c r="O4" t="n">
-        <v>4.852603295044026</v>
+        <v>4.846503516591936</v>
       </c>
       <c r="P4" t="n">
-        <v>387.6909861404339</v>
+        <v>387.6982009746711</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18027,28 +18073,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1982236321547548</v>
+        <v>0.1992660004734724</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1255969558606692</v>
+        <v>0.1273302640874733</v>
       </c>
       <c r="M5" t="n">
-        <v>3.029426651611963</v>
+        <v>3.026193563457518</v>
       </c>
       <c r="N5" t="n">
-        <v>15.06684744932238</v>
+        <v>15.036198597966</v>
       </c>
       <c r="O5" t="n">
-        <v>3.881603721314475</v>
+        <v>3.877653749107314</v>
       </c>
       <c r="P5" t="n">
-        <v>384.6696214557873</v>
+        <v>384.6589479426809</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18105,28 +18151,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.100359234590304</v>
+        <v>0.1006419689632899</v>
       </c>
       <c r="J6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04064773579491365</v>
+        <v>0.04109649151247918</v>
       </c>
       <c r="M6" t="n">
-        <v>2.873567147249666</v>
+        <v>2.867082102263153</v>
       </c>
       <c r="N6" t="n">
-        <v>13.09288673598741</v>
+        <v>13.05815382459837</v>
       </c>
       <c r="O6" t="n">
-        <v>3.618409420724444</v>
+        <v>3.613606761201109</v>
       </c>
       <c r="P6" t="n">
-        <v>381.7224409167358</v>
+        <v>381.7195458085657</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18183,28 +18229,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004236628333212079</v>
+        <v>0.005902643167936147</v>
       </c>
       <c r="J7" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K7" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L7" t="n">
-        <v>9.496656794605318e-05</v>
+        <v>0.0001849481608469095</v>
       </c>
       <c r="M7" t="n">
-        <v>2.580800023953902</v>
+        <v>2.582131319500593</v>
       </c>
       <c r="N7" t="n">
-        <v>10.40896931735656</v>
+        <v>10.40677303408964</v>
       </c>
       <c r="O7" t="n">
-        <v>3.226293433238298</v>
+        <v>3.225953042759557</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1874359645483</v>
+        <v>383.1703765136282</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18261,28 +18307,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.003127242623997395</v>
+        <v>-0.0008865837859380679</v>
       </c>
       <c r="J8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K8" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L8" t="n">
-        <v>4.043478920234822e-05</v>
+        <v>3.257655982635832e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.954618409280912</v>
+        <v>2.959039306268474</v>
       </c>
       <c r="N8" t="n">
-        <v>13.32077195973056</v>
+        <v>13.33172371129437</v>
       </c>
       <c r="O8" t="n">
-        <v>3.649763274478299</v>
+        <v>3.651263303473795</v>
       </c>
       <c r="P8" t="n">
-        <v>383.5072803986334</v>
+        <v>383.4843367797174</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18339,28 +18385,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03563726161091413</v>
+        <v>-0.03281938847357883</v>
       </c>
       <c r="J9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006343810397732352</v>
+        <v>0.005380573563136037</v>
       </c>
       <c r="M9" t="n">
-        <v>2.715677558201913</v>
+        <v>2.721695027377185</v>
       </c>
       <c r="N9" t="n">
-        <v>10.95654387904417</v>
+        <v>11.00126694932899</v>
       </c>
       <c r="O9" t="n">
-        <v>3.310067050536011</v>
+        <v>3.316815784653858</v>
       </c>
       <c r="P9" t="n">
-        <v>380.2149309569181</v>
+        <v>380.1860768510102</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18398,7 +18444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J369"/>
+  <dimension ref="A1:J370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37589,6 +37635,58 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-36.727554901876765,175.68603493208013</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-36.72767738897271,175.68692321697898</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-36.72766059673829,175.68780735074716</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-36.7276394626116,175.68868126904025</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-36.72768081511849,175.6895850719613</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-36.727676103876234,175.69048576386785</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-36.72765984789898,175.6913687685504</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-36.727631449936524,175.6922567763473</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:J372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13762,6 +13762,78 @@
         <v>384.54</v>
       </c>
       <c r="J370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>381.72</v>
+      </c>
+      <c r="C371" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="D371" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="E371" t="n">
+        <v>388.37</v>
+      </c>
+      <c r="F371" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="G371" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="H371" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="I371" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="C372" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="D372" t="n">
+        <v>386.43</v>
+      </c>
+      <c r="E372" t="n">
+        <v>388.76</v>
+      </c>
+      <c r="F372" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="G372" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="H372" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="I372" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="J372" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13778,7 +13850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17671,6 +17743,26 @@
       </c>
       <c r="B389" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -17839,28 +17931,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1499336948152963</v>
+        <v>0.1463705243884739</v>
       </c>
       <c r="J2" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K2" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05862556117121553</v>
+        <v>0.05648755025976027</v>
       </c>
       <c r="M2" t="n">
-        <v>3.431818872286606</v>
+        <v>3.430529475453107</v>
       </c>
       <c r="N2" t="n">
-        <v>19.94468794763343</v>
+        <v>19.89751865368351</v>
       </c>
       <c r="O2" t="n">
-        <v>4.465947597949783</v>
+        <v>4.460663476847756</v>
       </c>
       <c r="P2" t="n">
-        <v>381.4375997442826</v>
+        <v>381.4742096189045</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17917,28 +18009,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1715500140204397</v>
+        <v>0.1604057602941303</v>
       </c>
       <c r="J3" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K3" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06049096743423088</v>
+        <v>0.05272296557866163</v>
       </c>
       <c r="M3" t="n">
-        <v>4.099901408754627</v>
+        <v>4.134447383570797</v>
       </c>
       <c r="N3" t="n">
-        <v>25.25488035499406</v>
+        <v>25.70477855049939</v>
       </c>
       <c r="O3" t="n">
-        <v>5.025423400569752</v>
+        <v>5.069988022717548</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4700636885503</v>
+        <v>381.5845691487363</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17995,28 +18087,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1406098650762428</v>
+        <v>0.134397007816326</v>
       </c>
       <c r="J4" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K4" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04444115382874203</v>
+        <v>0.04090501490093623</v>
       </c>
       <c r="M4" t="n">
-        <v>3.928039897753937</v>
+        <v>3.938511594253182</v>
       </c>
       <c r="N4" t="n">
-        <v>23.488596336338</v>
+        <v>23.5483798827952</v>
       </c>
       <c r="O4" t="n">
-        <v>4.846503516591936</v>
+        <v>4.852667295704003</v>
       </c>
       <c r="P4" t="n">
-        <v>387.6982009746711</v>
+        <v>387.7620330527234</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18073,28 +18165,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1992660004734724</v>
+        <v>0.1978557244989256</v>
       </c>
       <c r="J5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1273302640874733</v>
+        <v>0.1269836047923368</v>
       </c>
       <c r="M5" t="n">
-        <v>3.026193563457518</v>
+        <v>3.017335881483014</v>
       </c>
       <c r="N5" t="n">
-        <v>15.036198597966</v>
+        <v>14.96472557440516</v>
       </c>
       <c r="O5" t="n">
-        <v>3.877653749107314</v>
+        <v>3.868426757017012</v>
       </c>
       <c r="P5" t="n">
-        <v>384.6589479426809</v>
+        <v>384.6734374368276</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18151,28 +18243,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1006419689632899</v>
+        <v>0.09791267316685058</v>
       </c>
       <c r="J6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04109649151247918</v>
+        <v>0.03932134026605127</v>
       </c>
       <c r="M6" t="n">
-        <v>2.867082102263153</v>
+        <v>2.8665382465077</v>
       </c>
       <c r="N6" t="n">
-        <v>13.05815382459837</v>
+        <v>13.0234010642692</v>
       </c>
       <c r="O6" t="n">
-        <v>3.613606761201109</v>
+        <v>3.608794960131319</v>
       </c>
       <c r="P6" t="n">
-        <v>381.7195458085657</v>
+        <v>381.7475875840269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18229,28 +18321,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005902643167936147</v>
+        <v>0.005676569263909722</v>
       </c>
       <c r="J7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001849481608469095</v>
+        <v>0.0001730668928464629</v>
       </c>
       <c r="M7" t="n">
-        <v>2.582131319500593</v>
+        <v>2.56934722447702</v>
       </c>
       <c r="N7" t="n">
-        <v>10.40677303408964</v>
+        <v>10.35093273285506</v>
       </c>
       <c r="O7" t="n">
-        <v>3.225953042759557</v>
+        <v>3.217286548141936</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1703765136282</v>
+        <v>383.1726990892192</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18307,28 +18399,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0008865837859380679</v>
+        <v>0.001085020665088804</v>
       </c>
       <c r="J8" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K8" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L8" t="n">
-        <v>3.257655982635832e-06</v>
+        <v>4.929672457798517e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.959039306268474</v>
+        <v>2.953901093429998</v>
       </c>
       <c r="N8" t="n">
-        <v>13.33172371129437</v>
+        <v>13.27860899793619</v>
       </c>
       <c r="O8" t="n">
-        <v>3.651263303473795</v>
+        <v>3.643982573769555</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4843367797174</v>
+        <v>383.4640770804594</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18385,28 +18477,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03281938847357883</v>
+        <v>-0.02982056443150848</v>
       </c>
       <c r="J9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005380573563136037</v>
+        <v>0.00448122136288176</v>
       </c>
       <c r="M9" t="n">
-        <v>2.721695027377185</v>
+        <v>2.721214397535805</v>
       </c>
       <c r="N9" t="n">
-        <v>11.00126694932899</v>
+        <v>10.98453169493924</v>
       </c>
       <c r="O9" t="n">
-        <v>3.316815784653858</v>
+        <v>3.314292035252663</v>
       </c>
       <c r="P9" t="n">
-        <v>380.1860768510102</v>
+        <v>380.1552630696292</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18444,7 +18536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:J372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37687,6 +37779,110 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-36.727585325740876,175.68603164562364</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-36.72771912082349,175.68691870931866</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-36.72770958076377,175.68780552985987</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-36.72767043026215,175.68868269923598</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-36.72771143311187,175.68958607747874</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-36.72770636818368,175.69048637749276</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-36.727682954489914,175.6913705623857</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-36.72765449127708,175.69225958067528</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-36.72758003073209,175.6860322176029</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-36.72771445403588,175.6869192134013</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-36.72769346285837,175.68780612901216</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-36.72766691939481,175.6886825370916</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-36.727705849830734,175.68958589411957</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-36.72770528731556,175.69048635557758</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-36.72767791959074,175.69137017151095</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-36.727651263696316,175.692259187851</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13834,6 +13834,78 @@
         <v>382.33</v>
       </c>
       <c r="J372" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="C373" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="D373" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="E373" t="n">
+        <v>388.36</v>
+      </c>
+      <c r="F373" t="n">
+        <v>382.29</v>
+      </c>
+      <c r="G373" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="H373" t="n">
+        <v>385.56</v>
+      </c>
+      <c r="I373" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="C374" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="D374" t="n">
+        <v>386.11</v>
+      </c>
+      <c r="E374" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="F374" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="G374" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="H374" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="I374" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="J374" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13850,7 +13922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17763,6 +17835,26 @@
       </c>
       <c r="B391" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17931,28 +18023,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1463705243884739</v>
+        <v>0.142277768537435</v>
       </c>
       <c r="J2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05648755025976027</v>
+        <v>0.05390898545905054</v>
       </c>
       <c r="M2" t="n">
-        <v>3.430529475453107</v>
+        <v>3.431825860719088</v>
       </c>
       <c r="N2" t="n">
-        <v>19.89751865368351</v>
+        <v>19.87905197037475</v>
       </c>
       <c r="O2" t="n">
-        <v>4.460663476847756</v>
+        <v>4.458593048302878</v>
       </c>
       <c r="P2" t="n">
-        <v>381.4742096189045</v>
+        <v>381.5165030392146</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18009,28 +18101,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1604057602941303</v>
+        <v>0.1509405475387629</v>
       </c>
       <c r="J3" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05272296557866163</v>
+        <v>0.04675053674598351</v>
       </c>
       <c r="M3" t="n">
-        <v>4.134447383570797</v>
+        <v>4.160090947229574</v>
       </c>
       <c r="N3" t="n">
-        <v>25.70477855049939</v>
+        <v>25.99450966913284</v>
       </c>
       <c r="O3" t="n">
-        <v>5.069988022717548</v>
+        <v>5.098481113933133</v>
       </c>
       <c r="P3" t="n">
-        <v>381.5845691487363</v>
+        <v>381.6823554005919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18087,28 +18179,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.134397007816326</v>
+        <v>0.129589007680867</v>
       </c>
       <c r="J4" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04090501490093623</v>
+        <v>0.03839595412546037</v>
       </c>
       <c r="M4" t="n">
-        <v>3.938511594253182</v>
+        <v>3.941677979604682</v>
       </c>
       <c r="N4" t="n">
-        <v>23.5483798827952</v>
+        <v>23.53406594538212</v>
       </c>
       <c r="O4" t="n">
-        <v>4.852667295704003</v>
+        <v>4.851192218968665</v>
       </c>
       <c r="P4" t="n">
-        <v>387.7620330527234</v>
+        <v>387.8117084596574</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18165,28 +18257,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1978557244989256</v>
+        <v>0.1948858932991414</v>
       </c>
       <c r="J5" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1269836047923368</v>
+        <v>0.1245724512974111</v>
       </c>
       <c r="M5" t="n">
-        <v>3.017335881483014</v>
+        <v>3.016763134458238</v>
       </c>
       <c r="N5" t="n">
-        <v>14.96472557440516</v>
+        <v>14.93512379226599</v>
       </c>
       <c r="O5" t="n">
-        <v>3.868426757017012</v>
+        <v>3.864598788007105</v>
       </c>
       <c r="P5" t="n">
-        <v>384.6734374368276</v>
+        <v>384.7041306477835</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18243,28 +18335,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09791267316685058</v>
+        <v>0.09510691220243708</v>
       </c>
       <c r="J6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03932134026605127</v>
+        <v>0.03749463218931315</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8665382465077</v>
+        <v>2.866340864360184</v>
       </c>
       <c r="N6" t="n">
-        <v>13.0234010642692</v>
+        <v>12.99295833840313</v>
       </c>
       <c r="O6" t="n">
-        <v>3.608794960131319</v>
+        <v>3.604574640426126</v>
       </c>
       <c r="P6" t="n">
-        <v>381.7475875840269</v>
+        <v>381.7765787675645</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18321,28 +18413,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005676569263909722</v>
+        <v>0.005020441238832308</v>
       </c>
       <c r="J7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001730668928464629</v>
+        <v>0.0001369021205910315</v>
       </c>
       <c r="M7" t="n">
-        <v>2.56934722447702</v>
+        <v>2.559679741446907</v>
       </c>
       <c r="N7" t="n">
-        <v>10.35093273285506</v>
+        <v>10.300634114611</v>
       </c>
       <c r="O7" t="n">
-        <v>3.217286548141936</v>
+        <v>3.209460097058538</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1726990892192</v>
+        <v>383.1794853550164</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18399,28 +18491,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001085020665088804</v>
+        <v>0.002597256691947331</v>
       </c>
       <c r="J8" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L8" t="n">
-        <v>4.929672457798517e-06</v>
+        <v>2.855109883603824e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.953901093429998</v>
+        <v>2.946319209794675</v>
       </c>
       <c r="N8" t="n">
-        <v>13.27860899793619</v>
+        <v>13.22039223233939</v>
       </c>
       <c r="O8" t="n">
-        <v>3.643982573769555</v>
+        <v>3.635985730491718</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4640770804594</v>
+        <v>383.4484617908605</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18477,28 +18569,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02982056443150848</v>
+        <v>-0.02704451147380656</v>
       </c>
       <c r="J9" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00448122136288176</v>
+        <v>0.003718893791004541</v>
       </c>
       <c r="M9" t="n">
-        <v>2.721214397535805</v>
+        <v>2.719739531978209</v>
       </c>
       <c r="N9" t="n">
-        <v>10.98453169493924</v>
+        <v>10.96418160287985</v>
       </c>
       <c r="O9" t="n">
-        <v>3.314292035252663</v>
+        <v>3.311220560892894</v>
       </c>
       <c r="P9" t="n">
-        <v>380.1552630696292</v>
+        <v>380.1265917670669</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18536,7 +18628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37883,6 +37975,110 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-36.72757617165789,175.68603263446914</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-36.72769865875475,175.68692091952676</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-36.727684818618584,175.68780645034522</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-36.72767052028439,175.68868270339354</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-36.72770413882523,175.68958583792886</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-36.72770258514525,175.6904863007896</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-36.7276782792264,175.69137019943062</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-36.72764884301074,175.69225889323283</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-36.727599146611254,175.6860301526605</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-36.72771032572377,175.6869196593205</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-36.72769634427163,175.68780602190114</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-36.727693565977695,175.68868376772653</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-36.72771521533457,175.68958620168982</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-36.72771645628613,175.69048658203465</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-36.727689607749554,175.6913710788989</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-36.72765960161329,175.69226020264716</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J374"/>
+  <dimension ref="A1:J377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13908,6 +13908,114 @@
       <c r="J374" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="C375" t="n">
+        <v>372.54</v>
+      </c>
+      <c r="D375" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="E375" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="F375" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="G375" t="n">
+        <v>381.37</v>
+      </c>
+      <c r="H375" t="n">
+        <v>380.54</v>
+      </c>
+      <c r="I375" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="C376" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="D376" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="E376" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="F376" t="n">
+        <v>381.01</v>
+      </c>
+      <c r="G376" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="H376" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="I376" t="n">
+        <v>377.51</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="C377" t="n">
+        <v>377.66</v>
+      </c>
+      <c r="D377" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="E377" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="F377" t="n">
+        <v>382.17</v>
+      </c>
+      <c r="G377" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="H377" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="I377" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13922,7 +14030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17855,6 +17963,36 @@
       </c>
       <c r="B393" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -18023,28 +18161,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.142277768537435</v>
+        <v>0.1323587149693878</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05390898545905054</v>
+        <v>0.04704761236446697</v>
       </c>
       <c r="M2" t="n">
-        <v>3.431825860719088</v>
+        <v>3.451551550673245</v>
       </c>
       <c r="N2" t="n">
-        <v>19.87905197037475</v>
+        <v>20.04651395554319</v>
       </c>
       <c r="O2" t="n">
-        <v>4.458593048302878</v>
+        <v>4.47733335318504</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5165030392146</v>
+        <v>381.6196489769704</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18101,28 +18239,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1509405475387629</v>
+        <v>0.1345936289123809</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04675053674598351</v>
+        <v>0.03694892506022329</v>
       </c>
       <c r="M3" t="n">
-        <v>4.160090947229574</v>
+        <v>4.212396002203296</v>
       </c>
       <c r="N3" t="n">
-        <v>25.99450966913284</v>
+        <v>26.67452409145575</v>
       </c>
       <c r="O3" t="n">
-        <v>5.098481113933133</v>
+        <v>5.164738530792798</v>
       </c>
       <c r="P3" t="n">
-        <v>381.6823554005919</v>
+        <v>381.8523425048782</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18179,28 +18317,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.129589007680867</v>
+        <v>0.1206363207098022</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03839595412546037</v>
+        <v>0.03362912927615347</v>
       </c>
       <c r="M4" t="n">
-        <v>3.941677979604682</v>
+        <v>3.955046344142798</v>
       </c>
       <c r="N4" t="n">
-        <v>23.53406594538212</v>
+        <v>23.62569191343494</v>
       </c>
       <c r="O4" t="n">
-        <v>4.851192218968665</v>
+        <v>4.860626699658691</v>
       </c>
       <c r="P4" t="n">
-        <v>387.8117084596574</v>
+        <v>387.9047977596684</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18257,28 +18395,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1948858932991414</v>
+        <v>0.1909829117443438</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1245724512974111</v>
+        <v>0.1216995296988055</v>
       </c>
       <c r="M5" t="n">
-        <v>3.016763134458238</v>
+        <v>3.013062768841165</v>
       </c>
       <c r="N5" t="n">
-        <v>14.93512379226599</v>
+        <v>14.87111041688081</v>
       </c>
       <c r="O5" t="n">
-        <v>3.864598788007105</v>
+        <v>3.856307873715584</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7041306477835</v>
+        <v>384.7447114369882</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18335,28 +18473,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09510691220243708</v>
+        <v>0.08967681687360646</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03749463218931315</v>
+        <v>0.03378126765270273</v>
       </c>
       <c r="M6" t="n">
-        <v>2.866340864360184</v>
+        <v>2.872339886262192</v>
       </c>
       <c r="N6" t="n">
-        <v>12.99295833840313</v>
+        <v>12.99451399819831</v>
       </c>
       <c r="O6" t="n">
-        <v>3.604574640426126</v>
+        <v>3.60479042361665</v>
       </c>
       <c r="P6" t="n">
-        <v>381.7765787675645</v>
+        <v>381.8330386393069</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18413,28 +18551,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005020441238832308</v>
+        <v>0.003348022579306907</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001369021205910315</v>
+        <v>6.188915721816457e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.559679741446907</v>
+        <v>2.547559276582951</v>
       </c>
       <c r="N7" t="n">
-        <v>10.300634114611</v>
+        <v>10.23140959136721</v>
       </c>
       <c r="O7" t="n">
-        <v>3.209460097058538</v>
+        <v>3.198657467026941</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1794853550164</v>
+        <v>383.1968699681622</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18491,28 +18629,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002597256691947331</v>
+        <v>-0.001281062594847772</v>
       </c>
       <c r="J8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L8" t="n">
-        <v>2.855109883603824e-05</v>
+        <v>7.042809848201159e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.946319209794675</v>
+        <v>2.940842430264639</v>
       </c>
       <c r="N8" t="n">
-        <v>13.22039223233939</v>
+        <v>13.16412028316446</v>
       </c>
       <c r="O8" t="n">
-        <v>3.635985730491718</v>
+        <v>3.628239281409712</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4484617908605</v>
+        <v>383.4887926782802</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18569,28 +18707,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02704451147380656</v>
+        <v>-0.02954928997460094</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003718893791004541</v>
+        <v>0.004506241365674124</v>
       </c>
       <c r="M9" t="n">
-        <v>2.719739531978209</v>
+        <v>2.711398750286223</v>
       </c>
       <c r="N9" t="n">
-        <v>10.96418160287985</v>
+        <v>10.89728611050547</v>
       </c>
       <c r="O9" t="n">
-        <v>3.311220560892894</v>
+        <v>3.301103771544522</v>
       </c>
       <c r="P9" t="n">
-        <v>380.1265917670669</v>
+        <v>380.1526447087516</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18628,7 +18766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J374"/>
+  <dimension ref="A1:J377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38079,6 +38217,162 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-36.727624544704156,175.68602740909733</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-36.72774308298287,175.68691612104763</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-36.72772200685843,175.68780506794354</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-36.72768933493245,175.68868357232157</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-36.727731154701644,175.68958672515112</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-36.727721500337346,175.69048668430565</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-36.72772341350093,175.69137370334613</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-36.727688560184916,175.6922637271563</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-36.72760883916968,175.68602910564715</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-36.72771678742968,175.68691896136</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-36.72769850533158,175.6878059415679</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-36.72767934246389,175.6886831108334</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-36.72771566559917,175.68958621647684</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-36.72771357397115,175.6904865235941</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-36.72771882814638,175.6913733473704</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-36.727694477416236,175.69226444733505</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.72759735169303,175.68603034655183</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.72769713307417,175.6869210843229</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.72768436839777,175.68780646708132</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.72766925997304,175.68868264518787</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-36.72770521946028,175.6895858734177</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-36.727705827749624,175.69048636653517</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-36.72771469233638,175.6913730262943</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-36.727692505005805,175.69226420727546</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J377"/>
+  <dimension ref="A1:J378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14014,6 +14014,42 @@
         <v>377.73</v>
       </c>
       <c r="J377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>381.27</v>
+      </c>
+      <c r="C378" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="D378" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="E378" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="F378" t="n">
+        <v>383.28</v>
+      </c>
+      <c r="G378" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="H378" t="n">
+        <v>382.49</v>
+      </c>
+      <c r="I378" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="J378" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14030,7 +14066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17993,6 +18029,16 @@
       </c>
       <c r="B396" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -18161,28 +18207,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1323587149693878</v>
+        <v>0.1303474807653619</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04704761236446697</v>
+        <v>0.04586052527317963</v>
       </c>
       <c r="M2" t="n">
-        <v>3.451551550673245</v>
+        <v>3.452124448044492</v>
       </c>
       <c r="N2" t="n">
-        <v>20.04651395554319</v>
+        <v>20.03278624532289</v>
       </c>
       <c r="O2" t="n">
-        <v>4.47733335318504</v>
+        <v>4.475800067621752</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6196489769704</v>
+        <v>381.6406272404923</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18239,28 +18285,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1345936289123809</v>
+        <v>0.131421374748851</v>
       </c>
       <c r="J3" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K3" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03694892506022329</v>
+        <v>0.03536047553059851</v>
       </c>
       <c r="M3" t="n">
-        <v>4.212396002203296</v>
+        <v>4.218222090475227</v>
       </c>
       <c r="N3" t="n">
-        <v>26.67452409145575</v>
+        <v>26.70190222527912</v>
       </c>
       <c r="O3" t="n">
-        <v>5.164738530792798</v>
+        <v>5.167388336991824</v>
       </c>
       <c r="P3" t="n">
-        <v>381.8523425048782</v>
+        <v>381.8854308362461</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18317,28 +18363,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1206363207098022</v>
+        <v>0.119407193647218</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03362912927615347</v>
+        <v>0.03313504429672587</v>
       </c>
       <c r="M4" t="n">
-        <v>3.955046344142798</v>
+        <v>3.950683692643209</v>
       </c>
       <c r="N4" t="n">
-        <v>23.62569191343494</v>
+        <v>23.57775664386022</v>
       </c>
       <c r="O4" t="n">
-        <v>4.860626699658691</v>
+        <v>4.855693219702025</v>
       </c>
       <c r="P4" t="n">
-        <v>387.9047977596684</v>
+        <v>387.9176182215368</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18395,28 +18441,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1909829117443438</v>
+        <v>0.1908708586466034</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1216995296988055</v>
+        <v>0.12219342542349</v>
       </c>
       <c r="M5" t="n">
-        <v>3.013062768841165</v>
+        <v>3.00565665248888</v>
       </c>
       <c r="N5" t="n">
-        <v>14.87111041688081</v>
+        <v>14.83178694145281</v>
       </c>
       <c r="O5" t="n">
-        <v>3.856307873715584</v>
+        <v>3.851205907433775</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7447114369882</v>
+        <v>384.7458802115686</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18473,28 +18519,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08967681687360646</v>
+        <v>0.08918902206132386</v>
       </c>
       <c r="J6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03378126765270273</v>
+        <v>0.03360892816946548</v>
       </c>
       <c r="M6" t="n">
-        <v>2.872339886262192</v>
+        <v>2.867304783755295</v>
       </c>
       <c r="N6" t="n">
-        <v>12.99451399819831</v>
+        <v>12.96236613740602</v>
       </c>
       <c r="O6" t="n">
-        <v>3.60479042361665</v>
+        <v>3.600328615196955</v>
       </c>
       <c r="P6" t="n">
-        <v>381.8330386393069</v>
+        <v>381.83812660375</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18551,28 +18597,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003348022579306907</v>
+        <v>0.003866537589264716</v>
       </c>
       <c r="J7" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K7" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L7" t="n">
-        <v>6.188915721816457e-05</v>
+        <v>8.300000593697288e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.547559276582951</v>
+        <v>2.543505281382307</v>
       </c>
       <c r="N7" t="n">
-        <v>10.23140959136721</v>
+        <v>10.2068923830627</v>
       </c>
       <c r="O7" t="n">
-        <v>3.198657467026941</v>
+        <v>3.194822746736147</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1968699681622</v>
+        <v>383.1914615753965</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18629,28 +18675,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001281062594847772</v>
+        <v>-0.001784367927034677</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L8" t="n">
-        <v>7.042809848201159e-06</v>
+        <v>1.374061091508061e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.940842430264639</v>
+        <v>2.935371852806195</v>
       </c>
       <c r="N8" t="n">
-        <v>13.16412028316446</v>
+        <v>13.1316724454638</v>
       </c>
       <c r="O8" t="n">
-        <v>3.628239281409712</v>
+        <v>3.623764954500194</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4887926782802</v>
+        <v>383.4940424258578</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18707,28 +18753,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02954928997460094</v>
+        <v>-0.03001847165533438</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004506241365674124</v>
+        <v>0.00467578292175197</v>
       </c>
       <c r="M9" t="n">
-        <v>2.711398750286223</v>
+        <v>2.706707135311825</v>
       </c>
       <c r="N9" t="n">
-        <v>10.89728611050547</v>
+        <v>10.87052748868241</v>
       </c>
       <c r="O9" t="n">
-        <v>3.301103771544522</v>
+        <v>3.297048299416072</v>
       </c>
       <c r="P9" t="n">
-        <v>380.1526447087516</v>
+        <v>380.1575385281379</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18766,7 +18812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J377"/>
+  <dimension ref="A1:J378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38373,6 +38419,58 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.7275893643069,175.6860312093682</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.72768214550625,175.6869227032028</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.72767257261221,175.68780690556704</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.72765917748218,175.68868217954255</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-36.727695223585975,175.68958554514577</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-36.72769528928544,175.69048615286206</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-36.72770588126289,175.69137234226275</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-36.72768596018934,175.69226341071416</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
